--- a/ИБ/5/frequency_original.xlsx
+++ b/ИБ/5/frequency_original.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0770AE7-5BFB-4AE0-85A1-A3D57230658B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C23FA09-A379-4AF2-A016-29CBA46AE32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Символ</t>
   </si>
@@ -112,7 +112,16 @@
     <t>Я</t>
   </si>
   <si>
-    <t>ПРОБЕЛ</t>
+    <t xml:space="preserve"> Пробел</t>
+  </si>
+  <si>
+    <t>Ф</t>
+  </si>
+  <si>
+    <t>Ш</t>
+  </si>
+  <si>
+    <t>Ъ</t>
   </si>
 </sst>
 </file>
@@ -182,6 +191,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Оригинальный</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> текст</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -237,7 +276,7 @@
               <c:strCache>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>ПРОБЕЛ</c:v>
+                  <c:v> Пробел</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>О</c:v>
@@ -333,98 +372,98 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>79</c:v>
+                  <c:v>948</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49</c:v>
+                  <c:v>588</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>48</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="25">
-                  <c:v>4</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B2CD-4FF0-9EF1-AB76336693CC}"/>
+              <c16:uniqueId val="{00000000-8ACB-4129-A1F2-D39CA4DD2286}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -438,11 +477,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="580957216"/>
-        <c:axId val="580950016"/>
+        <c:axId val="169232432"/>
+        <c:axId val="169228592"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="580957216"/>
+        <c:axId val="169232432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -485,7 +524,7 @@
             <a:endParaRPr lang="LID4096"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580950016"/>
+        <c:crossAx val="169228592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -493,7 +532,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="580950016"/>
+        <c:axId val="169228592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -544,7 +583,459 @@
             <a:endParaRPr lang="LID4096"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="580957216"/>
+        <c:crossAx val="169232432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Зашифрованный</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Frequency!$V$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Частота</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Frequency!$U$15:$U$40</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>С</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>И</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Г</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Л</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Х</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Р</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Ф</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>П</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Е</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>У</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>З</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>О</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Н</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>К</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Ш</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Ц</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Д</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Ж</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Ъ</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Т</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Я</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Ю</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Й</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Щ</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>М</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Ь</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Frequency!$V$15:$V$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>588</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B8E2-4C5A-BB27-B1DC42781BC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="98945808"/>
+        <c:axId val="98950608"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="98945808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="98950608"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="98950608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="98945808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -640,6 +1131,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -1143,27 +1674,530 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>156210</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>484203</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15647</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>156210</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>182362</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15647</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F292DE88-6DCE-194F-749E-DEFF06D78E0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82BEF099-4248-803D-C94C-75EEBBECF6CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1176,6 +2210,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>181253</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>506768</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>173114</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{792D9B1F-F264-B7B9-7E36-52E49478588F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1506,14 +2576,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1521,236 +2591,418 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
       <c r="B13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="U14" t="s">
+        <v>0</v>
+      </c>
+      <c r="V14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="U15" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="U16" t="s">
+        <v>10</v>
+      </c>
+      <c r="V16">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="U17" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
       <c r="B18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="U18" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="U19" t="s">
+        <v>22</v>
+      </c>
+      <c r="V19">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
       <c r="B20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="U20" t="s">
+        <v>18</v>
+      </c>
+      <c r="V20">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
       <c r="B21">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="U21" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="U22" t="s">
+        <v>17</v>
+      </c>
+      <c r="V22">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
       <c r="B23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="U23" t="s">
+        <v>7</v>
+      </c>
+      <c r="V23">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s">
+        <v>21</v>
+      </c>
+      <c r="V24">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="U25" t="s">
+        <v>9</v>
+      </c>
+      <c r="V25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="U26" t="s">
+        <v>16</v>
+      </c>
+      <c r="V26">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="U27" t="s">
+        <v>15</v>
+      </c>
+      <c r="V27">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
       <c r="B28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="U28" t="s">
+        <v>12</v>
+      </c>
+      <c r="V28">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>11</v>
       </c>
       <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="U29" t="s">
+        <v>32</v>
+      </c>
+      <c r="V29">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="U30" t="s">
+        <v>23</v>
+      </c>
+      <c r="V30">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U31" t="s">
+        <v>6</v>
+      </c>
+      <c r="V31">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="U32" t="s">
+        <v>8</v>
+      </c>
+      <c r="V32">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U33" t="s">
+        <v>33</v>
+      </c>
+      <c r="V33">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U34" t="s">
+        <v>20</v>
+      </c>
+      <c r="V34">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U35" t="s">
+        <v>29</v>
+      </c>
+      <c r="V35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U36" t="s">
+        <v>28</v>
+      </c>
+      <c r="V36">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U37" t="s">
+        <v>11</v>
+      </c>
+      <c r="V37">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U38" t="s">
+        <v>25</v>
+      </c>
+      <c r="V38">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U39" t="s">
+        <v>14</v>
+      </c>
+      <c r="V39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="21:22" x14ac:dyDescent="0.3">
+      <c r="U40" t="s">
+        <v>27</v>
+      </c>
+      <c r="V40">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
